--- a/data/trans_orig/IP19C03-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP19C03-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>6184</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2428</t>
+          <t>3033</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9894</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>5350</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13622</t>
+          <t>14261</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13380</t>
+          <t>13137</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18291</t>
+          <t>18201</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16624</t>
+          <t>16319</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24090</t>
+          <t>23485</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32217</t>
+          <t>31578</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40684</t>
+          <t>40489</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,33%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8053</t>
+          <t>7723</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>17604</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>9399</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20113</t>
+          <t>20070</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20262</t>
+          <t>19678</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35156</t>
+          <t>34319</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,08%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39041</t>
+          <t>39618</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49169</t>
+          <t>49499</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>44862</t>
+          <t>44905</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55547</t>
+          <t>55576</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>87041</t>
+          <t>87878</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>101935</t>
+          <t>102519</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,9%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5071</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13982</t>
+          <t>13975</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9436</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9380</t>
+          <t>9410</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20797</t>
+          <t>20566</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,54%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20310</t>
+          <t>20317</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29221</t>
+          <t>29044</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26008</t>
+          <t>25893</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32821</t>
+          <t>32477</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48824</t>
+          <t>49055</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>60241</t>
+          <t>60211</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,48%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5094</t>
+          <t>5772</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13489</t>
+          <t>13836</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2797</t>
+          <t>2661</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9996</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9925</t>
+          <t>10184</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20900</t>
+          <t>21197</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28470</t>
+          <t>28123</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36865</t>
+          <t>36187</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31645</t>
+          <t>31641</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38844</t>
+          <t>38980</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>62700</t>
+          <t>62403</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>73675</t>
+          <t>73416</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>87,82%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8436</t>
+          <t>8468</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>8535</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5457</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14610</t>
+          <t>14582</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,97%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17755</t>
+          <t>17723</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24208</t>
+          <t>24248</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14034</t>
+          <t>13932</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20375</t>
+          <t>20367</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34049</t>
+          <t>34077</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43202</t>
+          <t>43068</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,51%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>2693</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9809</t>
+          <t>9726</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5268</t>
+          <t>5203</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14075</t>
+          <t>13891</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,87%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15531</t>
+          <t>15614</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22486</t>
+          <t>22647</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21959</t>
+          <t>21555</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>27133</t>
+          <t>27141</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>39623</t>
+          <t>39807</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>48430</t>
+          <t>48495</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,31%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14438</t>
+          <t>14594</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5418</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14907</t>
+          <t>14446</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13122</t>
+          <t>12940</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25779</t>
+          <t>25986</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>50846</t>
+          <t>50690</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>60319</t>
+          <t>59913</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>53122</t>
+          <t>53583</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>62611</t>
+          <t>62570</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>107535</t>
+          <t>107328</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>120192</t>
+          <t>120374</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,29%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14136</t>
+          <t>14146</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26903</t>
+          <t>26400</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>9667</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20362</t>
+          <t>20258</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27299</t>
+          <t>27369</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>43000</t>
+          <t>43622</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>28,01%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>54417</t>
+          <t>54920</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>67184</t>
+          <t>67174</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>54051</t>
+          <t>54155</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>64728</t>
+          <t>64746</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>112734</t>
+          <t>112112</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>128435</t>
+          <t>128365</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,43%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>61716</t>
+          <t>62455</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>87218</t>
+          <t>85858</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>52195</t>
+          <t>52878</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>76163</t>
+          <t>75264</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>120886</t>
+          <t>119633</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>152067</t>
+          <t>152819</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,44%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>263712</t>
+          <t>265072</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>289214</t>
+          <t>288475</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>285568</t>
+          <t>286467</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>309536</t>
+          <t>308853</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>560594</t>
+          <t>559842</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>591775</t>
+          <t>593028</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,21%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7914</t>
+          <t>7821</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11876</t>
+          <t>12565</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>7154</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17253</t>
+          <t>17605</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>33,47%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14461</t>
+          <t>14554</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20846</t>
+          <t>20881</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18355</t>
+          <t>17666</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25968</t>
+          <t>25576</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35352</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45105</t>
+          <t>45451</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>86,4%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8734</t>
+          <t>8462</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6492</t>
+          <t>6346</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16602</t>
+          <t>16002</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10269</t>
+          <t>9498</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22149</t>
+          <t>21535</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>44310</t>
+          <t>44582</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51473</t>
+          <t>51076</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>41030</t>
+          <t>41630</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51140</t>
+          <t>51286</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>88528</t>
+          <t>89142</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>100408</t>
+          <t>101179</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>91,42%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7236</t>
+          <t>7747</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8680</t>
+          <t>8549</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4580</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12864</t>
+          <t>13234</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>18,15%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26227</t>
+          <t>25716</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32085</t>
+          <t>32083</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30765</t>
+          <t>30896</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37500</t>
+          <t>37496</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60044</t>
+          <t>59674</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>68328</t>
+          <t>68569</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>94,05%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>7149</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16694</t>
+          <t>16974</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>4350</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12661</t>
+          <t>12547</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13674</t>
+          <t>13387</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26175</t>
+          <t>26588</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24467</t>
+          <t>24187</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34148</t>
+          <t>34012</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28565</t>
+          <t>28679</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36938</t>
+          <t>36876</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>56212</t>
+          <t>55799</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68713</t>
+          <t>69000</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,75%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7374</t>
+          <t>6530</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5233</t>
+          <t>5785</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2699</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9610</t>
+          <t>9982</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,59%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18694</t>
+          <t>19538</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24700</t>
+          <t>24706</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22397</t>
+          <t>21845</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26986</t>
+          <t>26984</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>44088</t>
+          <t>43716</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50999</t>
+          <t>51348</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>3118</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10737</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1593</t>
+          <t>1540</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8968</t>
+          <t>8939</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6267</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16815</t>
+          <t>16684</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24689</t>
+          <t>25060</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32455</t>
+          <t>32308</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24191</t>
+          <t>24220</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31566</t>
+          <t>31619</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>51770</t>
+          <t>51901</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>62143</t>
+          <t>62318</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,86%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6529</t>
+          <t>6815</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17118</t>
+          <t>16875</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6524</t>
+          <t>6355</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16794</t>
+          <t>16180</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15235</t>
+          <t>15074</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29634</t>
+          <t>28905</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>46851</t>
+          <t>47094</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>57440</t>
+          <t>57154</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>50370</t>
+          <t>50984</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>60640</t>
+          <t>60809</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>101499</t>
+          <t>102228</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>115898</t>
+          <t>116059</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,51%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22342</t>
+          <t>21754</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>35829</t>
+          <t>34982</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16738</t>
+          <t>16629</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29653</t>
+          <t>29517</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>42435</t>
+          <t>42673</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>61508</t>
+          <t>60862</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,14%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>42018</t>
+          <t>42865</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>55505</t>
+          <t>56093</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>40434</t>
+          <t>40570</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>53349</t>
+          <t>53458</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>86426</t>
+          <t>87072</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>105499</t>
+          <t>105261</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,15%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>61062</t>
+          <t>60546</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>85384</t>
+          <t>84849</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>58221</t>
+          <t>59864</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>83474</t>
+          <t>83812</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>126829</t>
+          <t>125795</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>162877</t>
+          <t>161024</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>267969</t>
+          <t>268504</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>292291</t>
+          <t>292807</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>283100</t>
+          <t>282762</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>308353</t>
+          <t>306710</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>557050</t>
+          <t>558903</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>593098</t>
+          <t>594132</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,53%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4210</t>
+          <t>4421</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12477</t>
+          <t>12563</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>8569</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7718</t>
+          <t>7280</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17934</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>29,95%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16089</t>
+          <t>16003</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24356</t>
+          <t>24145</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21688</t>
+          <t>21342</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28083</t>
+          <t>28020</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40542</t>
+          <t>40960</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50758</t>
+          <t>51196</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>87,55%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6852</t>
+          <t>6868</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17489</t>
+          <t>16532</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11436</t>
+          <t>11387</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22139</t>
+          <t>22493</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20427</t>
+          <t>20980</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35080</t>
+          <t>36323</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36019</t>
+          <t>36976</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46656</t>
+          <t>46640</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35344</t>
+          <t>34990</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>46047</t>
+          <t>46096</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>75911</t>
+          <t>74668</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>90564</t>
+          <t>90011</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,1%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>671</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6435</t>
+          <t>6485</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>729</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>6799</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2248</t>
+          <t>2265</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10749</t>
+          <t>10425</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26082</t>
+          <t>26032</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31823</t>
+          <t>31846</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25308</t>
+          <t>25325</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31311</t>
+          <t>31395</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53892</t>
+          <t>54216</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>62393</t>
+          <t>62376</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,5%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15266</t>
+          <t>14385</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11702</t>
+          <t>11285</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10891</t>
+          <t>10677</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22569</t>
+          <t>22495</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,06%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31279</t>
+          <t>32160</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40597</t>
+          <t>40981</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39301</t>
+          <t>39718</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>47858</t>
+          <t>47790</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>74979</t>
+          <t>75053</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>86657</t>
+          <t>86871</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>89,05%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7553</t>
+          <t>7913</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>7256</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4593</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12465</t>
+          <t>12606</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>39,26%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7491</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>13121</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9790</t>
+          <t>9812</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15659</t>
+          <t>15672</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19646</t>
+          <t>19505</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27518</t>
+          <t>27535</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,75%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>634</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5711</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1498</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7773</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2857</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10224</t>
+          <t>10787</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34032</t>
+          <t>34329</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>39097</t>
+          <t>39109</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32797</t>
+          <t>31699</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39082</t>
+          <t>39072</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>70089</t>
+          <t>69526</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>77456</t>
+          <t>77432</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1343</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7683</t>
+          <t>7860</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4084</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13824</t>
+          <t>13341</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6502</t>
+          <t>6718</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18275</t>
+          <t>18099</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>59760</t>
+          <t>59583</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>66100</t>
+          <t>66120</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>48119</t>
+          <t>48602</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>57859</t>
+          <t>58033</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>111111</t>
+          <t>111287</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>122884</t>
+          <t>122668</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,81%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15526</t>
+          <t>14522</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27299</t>
+          <t>27293</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15117</t>
+          <t>14923</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27765</t>
+          <t>28229</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33271</t>
+          <t>33709</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>51681</t>
+          <t>51575</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,66%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>51953</t>
+          <t>51959</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>63726</t>
+          <t>64730</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>50893</t>
+          <t>50429</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>63541</t>
+          <t>63735</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>106229</t>
+          <t>106335</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>124639</t>
+          <t>124201</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>78,65%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>50723</t>
+          <t>51337</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>73943</t>
+          <t>73260</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>54839</t>
+          <t>55840</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>79158</t>
+          <t>81047</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>113958</t>
+          <t>112577</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>147795</t>
+          <t>145356</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>288675</t>
+          <t>289358</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>311895</t>
+          <t>311281</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>289600</t>
+          <t>287711</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>313919</t>
+          <t>312918</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>583581</t>
+          <t>586020</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>617418</t>
+          <t>618799</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,61%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7999</t>
+          <t>7776</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17660</t>
+          <t>17473</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7947</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18408</t>
+          <t>18385</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18337</t>
+          <t>17781</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33067</t>
+          <t>32969</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,15%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17158</t>
+          <t>17345</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26819</t>
+          <t>27042</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21457</t>
+          <t>21480</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31918</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41615</t>
+          <t>41713</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56345</t>
+          <t>56901</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>76,19%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11940</t>
+          <t>11988</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28983</t>
+          <t>27872</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11378</t>
+          <t>10648</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26809</t>
+          <t>25902</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26889</t>
+          <t>27224</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48138</t>
+          <t>49112</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,42%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39861</t>
+          <t>40972</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56904</t>
+          <t>56856</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47020</t>
+          <t>47927</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>62451</t>
+          <t>63181</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>94535</t>
+          <t>93561</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>115784</t>
+          <t>115449</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>80,92%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5760</t>
+          <t>6372</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2798</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10995</t>
+          <t>10699</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4356</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13797</t>
+          <t>14313</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,91%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26063</t>
+          <t>25451</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30781</t>
+          <t>30754</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29057</t>
+          <t>29353</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37254</t>
+          <t>37169</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>58077</t>
+          <t>57561</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>67518</t>
+          <t>67171</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,46%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14124</t>
+          <t>14230</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15865</t>
+          <t>16708</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9341</t>
+          <t>9357</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25837</t>
+          <t>24676</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>24,31%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28719</t>
+          <t>28613</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38531</t>
+          <t>38509</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42796</t>
+          <t>41953</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56219</t>
+          <t>55663</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>75667</t>
+          <t>76828</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>92163</t>
+          <t>92147</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,78%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2204</t>
+          <t>1958</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7227</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1699</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8032</t>
+          <t>8047</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>4871</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13123</t>
+          <t>12663</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18065</t>
+          <t>18113</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23088</t>
+          <t>23334</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26595</t>
+          <t>26580</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32928</t>
+          <t>32865</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>46796</t>
+          <t>47256</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54633</t>
+          <t>55048</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,87%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>5922</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7513</t>
+          <t>7317</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10396</t>
+          <t>10464</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21005</t>
+          <t>21040</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25888</t>
+          <t>25892</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19431</t>
+          <t>19627</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25670</t>
+          <t>25637</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>43511</t>
+          <t>43443</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>50621</t>
+          <t>50811</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,26%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8940</t>
+          <t>8827</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21152</t>
+          <t>20587</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14609</t>
+          <t>13593</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30106</t>
+          <t>30053</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>26916</t>
+          <t>27531</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46730</t>
+          <t>46379</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>56604</t>
+          <t>57169</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>68816</t>
+          <t>68929</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>78582</t>
+          <t>78635</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>94079</t>
+          <t>95095</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>139714</t>
+          <t>140065</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>159528</t>
+          <t>158913</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,23%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>2445</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10704</t>
+          <t>9862</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2948</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11655</t>
+          <t>11834</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6643</t>
+          <t>6671</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17769</t>
+          <t>17488</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>72591</t>
+          <t>73433</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>80792</t>
+          <t>80850</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>90122</t>
+          <t>89943</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>98888</t>
+          <t>98829</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>167303</t>
+          <t>167584</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>178429</t>
+          <t>178401</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>56430</t>
+          <t>54937</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>84026</t>
+          <t>82922</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>65330</t>
+          <t>63316</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>96364</t>
+          <t>94934</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>126168</t>
+          <t>129528</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>169935</t>
+          <t>169743</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>307607</t>
+          <t>308711</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>335203</t>
+          <t>336696</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>388080</t>
+          <t>389510</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>419114</t>
+          <t>421128</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>706141</t>
+          <t>706333</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>749908</t>
+          <t>746548</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,21%</t>
         </is>
       </c>
     </row>
